--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IZAC TOP BRASIL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trans\Documents\GitHub\repo-viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBABA97C-0902-4615-A29B-F8F95966D0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636AAFDC-A485-4923-A96A-23D6D4E136F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ficha Cadastral" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Ficha Cadastral'!$A$1:$P$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -676,7 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -738,269 +737,260 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1079,10 +1069,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1376,27 +1362,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.21875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="4.44140625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="10" customWidth="1"/>
-    <col min="9" max="10" width="4.5546875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="10" customWidth="1"/>
+    <col min="9" max="10" width="4.5703125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="10" customWidth="1"/>
     <col min="12" max="12" width="11" style="10" customWidth="1"/>
-    <col min="13" max="13" width="3.109375" style="10" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="24.88671875" style="10" customWidth="1"/>
-    <col min="16" max="17" width="5.109375" style="10" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="1"/>
+    <col min="13" max="13" width="3.140625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="10" customWidth="1"/>
+    <col min="15" max="15" width="24.85546875" style="10" customWidth="1"/>
+    <col min="16" max="17" width="5.140625" style="10" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1415,7 +1401,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1434,7 +1420,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:17" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1453,7 +1439,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" ht="81.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="81.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1472,9 +1458,9 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="46"/>
-    </row>
-    <row r="5" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1482,22 +1468,22 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="90" t="s">
+      <c r="H5" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="92"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="66"/>
       <c r="L5" s="68" t="s">
         <v>6</v>
       </c>
       <c r="M5" s="68"/>
       <c r="N5" s="68"/>
-      <c r="O5" s="64"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="9"/>
-      <c r="Q5" s="46"/>
-    </row>
-    <row r="6" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1505,22 +1491,22 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="90" t="s">
+      <c r="H6" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="61" t="s">
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
       <c r="P6" s="9"/>
-      <c r="Q6" s="46"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1528,22 +1514,22 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="90" t="s">
+      <c r="H7" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="83" t="s">
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="46"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1551,22 +1537,22 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="94"/>
-      <c r="J8" s="76" t="s">
+      <c r="I8" s="71"/>
+      <c r="J8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="89"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
       <c r="P8" s="9"/>
-      <c r="Q8" s="46"/>
-    </row>
-    <row r="9" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1574,18 +1560,18 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="65"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="28"/>
       <c r="P9" s="9"/>
-      <c r="Q9" s="46"/>
-    </row>
-    <row r="10" spans="1:17" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>31</v>
       </c>
@@ -1595,22 +1581,22 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="90" t="s">
+      <c r="H10" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="92"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="95" t="s">
+      <c r="I10" s="66"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="O10" s="84"/>
+      <c r="O10" s="36"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="46"/>
-    </row>
-    <row r="11" spans="1:17" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1618,22 +1604,22 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="96" t="s">
+      <c r="H11" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="97"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="95" t="s">
+      <c r="I11" s="64"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="105" t="s">
         <v>5</v>
       </c>
       <c r="O11" s="12"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="46"/>
-    </row>
-    <row r="12" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1649,236 +1635,235 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="46"/>
-    </row>
-    <row r="13" spans="1:17" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q12" s="2"/>
+    </row>
+    <row r="13" spans="1:17" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="100"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="94"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="46"/>
-    </row>
-    <row r="14" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
       <c r="P14" s="9"/>
-      <c r="Q14" s="46"/>
-    </row>
-    <row r="15" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="41" t="s">
+      <c r="C15" s="48"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="40" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="21" t="s">
         <v>11</v>
       </c>
       <c r="O15" s="13"/>
       <c r="P15" s="9"/>
-      <c r="Q15" s="46"/>
-    </row>
-    <row r="16" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="46"/>
-    </row>
-    <row r="17" spans="1:17" s="69" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="78"/>
-      <c r="B17" s="43" t="s">
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="33"/>
+      <c r="B17" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="79"/>
-      <c r="Q17" s="51"/>
-    </row>
-    <row r="18" spans="1:17" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="78"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="46"/>
-    </row>
-    <row r="19" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="34"/>
+    </row>
+    <row r="18" spans="1:17" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="33"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="101"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="102" t="s">
+      <c r="C19" s="77"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="103"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="40" t="s">
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="O19" s="105" t="s">
+      <c r="O19" s="22" t="s">
         <v>15</v>
       </c>
       <c r="P19" s="9"/>
-      <c r="Q19" s="46"/>
-    </row>
-    <row r="20" spans="1:17" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="70"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="87"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="53"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="26"/>
       <c r="P20" s="9"/>
-      <c r="Q20" s="46"/>
-    </row>
-    <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="48"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="24"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
-      <c r="Q21" s="46"/>
-    </row>
-    <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21" s="2"/>
+    </row>
+    <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="48"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="24"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="46"/>
-    </row>
-    <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="48"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="24"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="46"/>
-    </row>
-    <row r="24" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q23" s="2"/>
+    </row>
+    <row r="24" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -1895,30 +1880,30 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="46"/>
-    </row>
-    <row r="25" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q24" s="2"/>
+    </row>
+    <row r="25" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="45"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="81"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="46"/>
-    </row>
-    <row r="26" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q25" s="2"/>
+    </row>
+    <row r="26" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1935,53 +1920,53 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="9"/>
-      <c r="Q26" s="46"/>
-    </row>
-    <row r="27" spans="1:17" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" spans="1:17" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
       <c r="P27" s="9"/>
-      <c r="Q27" s="46"/>
-    </row>
-    <row r="28" spans="1:17" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="28" spans="1:17" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="41" t="s">
+      <c r="C28" s="48"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="42"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="24"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="50"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="46"/>
-    </row>
-    <row r="29" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q28" s="2"/>
+    </row>
+    <row r="29" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1998,30 +1983,30 @@
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="46"/>
-    </row>
-    <row r="30" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q29" s="2"/>
+    </row>
+    <row r="30" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="45"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="81"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="46"/>
-    </row>
-    <row r="31" spans="1:17" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q30" s="2"/>
+    </row>
+    <row r="31" spans="1:17" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -2038,114 +2023,114 @@
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="46"/>
-    </row>
-    <row r="32" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="32" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
-      <c r="B32" s="106" t="s">
+      <c r="B32" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="107"/>
-      <c r="H32" s="108"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="30"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="100"/>
+      <c r="N32" s="100"/>
+      <c r="O32" s="101"/>
       <c r="P32" s="9"/>
-      <c r="Q32" s="46"/>
-    </row>
-    <row r="33" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q32" s="2"/>
+    </row>
+    <row r="33" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
-      <c r="B33" s="106" t="s">
+      <c r="B33" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="108"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="26"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="97"/>
       <c r="P33" s="9"/>
-      <c r="Q33" s="46"/>
-    </row>
-    <row r="34" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q33" s="2"/>
+    </row>
+    <row r="34" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="106" t="s">
+      <c r="B34" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="107"/>
-      <c r="H34" s="108"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="28"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
+      <c r="N34" s="98"/>
+      <c r="O34" s="99"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="46"/>
-    </row>
-    <row r="35" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q34" s="2"/>
+    </row>
+    <row r="35" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="106" t="s">
+      <c r="B35" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="107"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="26"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="97"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="46"/>
-    </row>
-    <row r="36" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q35" s="2"/>
+    </row>
+    <row r="36" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
-      <c r="B36" s="106" t="s">
+      <c r="B36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="107"/>
-      <c r="G36" s="107"/>
-      <c r="H36" s="108"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="97"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="46"/>
-    </row>
-    <row r="37" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q36" s="2"/>
+    </row>
+    <row r="37" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2162,9 +2147,9 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="46"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q37" s="2"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2181,28 +2166,28 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="9"/>
-      <c r="Q38" s="46"/>
-    </row>
-    <row r="39" spans="1:17" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="1:17" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="77"/>
+      <c r="F39" s="32"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
-      <c r="Q39" s="46"/>
-    </row>
-    <row r="40" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q39" s="2"/>
+    </row>
+    <row r="40" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2215,17 +2200,17 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="21" t="s">
+      <c r="K40" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="62"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
-      <c r="Q40" s="46"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q40" s="2"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2242,9 +2227,9 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="9"/>
-      <c r="Q41" s="46"/>
-    </row>
-    <row r="42" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q41" s="2"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="18"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -2261,9 +2246,9 @@
       <c r="N42" s="19"/>
       <c r="O42" s="19"/>
       <c r="P42" s="20"/>
-      <c r="Q42" s="46"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q42" s="2"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2282,7 +2267,7 @@
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2301,7 +2286,7 @@
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2320,7 +2305,7 @@
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2339,7 +2324,7 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2358,7 +2343,7 @@
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2379,6 +2364,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="B25:O25"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B13:O13"/>
+    <mergeCell ref="B16:O16"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E18:L18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="L7:O7"/>
     <mergeCell ref="B36:H36"/>
     <mergeCell ref="J11:M11"/>
     <mergeCell ref="J10:M10"/>
@@ -2395,47 +2417,10 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="H9:I9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E18:L18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B17:O17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B13:O13"/>
-    <mergeCell ref="B16:O16"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="B25:O25"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="I36:O36"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="72" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="73" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trans\Documents\GitHub\repo-viatop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felp\Documents\viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636AAFDC-A485-4923-A96A-23D6D4E136F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA30889-CE1B-445D-AA5C-48CCD134142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ficha Cadastral" sheetId="1" r:id="rId1"/>
@@ -275,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -485,31 +485,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -518,95 +501,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -614,60 +508,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -675,7 +515,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -710,9 +550,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -737,12 +574,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -767,7 +598,7 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -782,192 +613,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -980,17 +640,140 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1021,15 +804,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>86018</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>292</xdr:rowOff>
+      <xdr:colOff>95543</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>122945</xdr:colOff>
+      <xdr:colOff>132470</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>136560</xdr:rowOff>
+      <xdr:rowOff>41310</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1058,8 +841,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="86018" y="1810042"/>
-          <a:ext cx="3308252" cy="1268131"/>
+          <a:off x="95543" y="1724317"/>
+          <a:ext cx="3218277" cy="1250693"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1439,7 +1222,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" ht="81.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1460,7 +1243,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1468,22 +1251,22 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="65" t="s">
+      <c r="H5" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="68" t="s">
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="69"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="56"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1491,22 +1274,22 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="42" t="s">
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1514,22 +1297,22 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="65" t="s">
+      <c r="H7" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="72" t="s">
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1537,22 +1320,22 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="70" t="s">
+      <c r="H8" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="71"/>
-      <c r="J8" s="44" t="s">
+      <c r="I8" s="74"/>
+      <c r="J8" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1560,18 +1343,18 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="62"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="28"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="25"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>31</v>
       </c>
@@ -1581,22 +1364,22 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="65" t="s">
+      <c r="H10" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="66"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="105" t="s">
+      <c r="I10" s="74"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="O10" s="36"/>
+      <c r="O10" s="85"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1604,22 +1387,22 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="63" t="s">
+      <c r="H11" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="105" t="s">
+      <c r="I11" s="74"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="12"/>
+      <c r="O11" s="86"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1637,151 +1420,151 @@
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="94"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="76"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="47" t="s">
+      <c r="C15" s="77"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="21" t="s">
+      <c r="H15" s="77"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="O15" s="12"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
+    <row r="17" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
       <c r="B17" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="80"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="34"/>
-    </row>
-    <row r="18" spans="1:17" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="35"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="31"/>
+    </row>
+    <row r="18" spans="1:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="32"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="77" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="77"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="89" t="s">
+      <c r="D19" s="77"/>
+      <c r="E19" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="21" t="s">
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="O19" s="22" t="s">
+      <c r="O19" s="78" t="s">
         <v>15</v>
       </c>
       <c r="P19" s="9"/>
@@ -1789,121 +1572,121 @@
     </row>
     <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="26"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="23"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="24"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="21"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="24"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="21"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="24"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="21"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="81"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="79"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1922,211 +1705,211 @@
       <c r="P26" s="9"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="78"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="47" t="s">
+      <c r="C28" s="77"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="48"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="50"/>
+      <c r="L28" s="77"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="69"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:17" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="80"/>
-      <c r="M30" s="80"/>
-      <c r="N30" s="80"/>
-      <c r="O30" s="81"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:17" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="100"/>
-      <c r="N32" s="100"/>
-      <c r="O32" s="101"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="41"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
     </row>
-    <row r="33" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="97"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="37"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="35"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
     </row>
-    <row r="34" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="98"/>
-      <c r="O34" s="99"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="39"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
     </row>
-    <row r="35" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="96"/>
-      <c r="K35" s="96"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="97"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="35"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
     </row>
-    <row r="36" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="97"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="103"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="103"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
     </row>
@@ -2172,17 +1955,17 @@
       <c r="A39" s="8"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="20"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="32"/>
+      <c r="F39" s="29"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="102"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
@@ -2191,21 +1974,21 @@
       <c r="A40" s="8"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="17"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="62" t="s">
+      <c r="K40" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="62"/>
-      <c r="M40" s="62"/>
-      <c r="N40" s="62"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="34"/>
+      <c r="N40" s="34"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
@@ -2230,22 +2013,22 @@
       <c r="Q41" s="2"/>
     </row>
     <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="20"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="19"/>
       <c r="Q42" s="2"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2364,19 +2147,25 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="B25:O25"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:M15"/>
     <mergeCell ref="B27:C27"/>
@@ -2391,32 +2180,26 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E19:M19"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="D27:O27"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B25:O25"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:O32"/>
     <mergeCell ref="D28:J28"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="M28:O28"/>
-    <mergeCell ref="D27:O27"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felp\Documents\viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA30889-CE1B-445D-AA5C-48CCD134142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6575F1-0E79-4393-BC17-9E63E7D70BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,14 +209,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
-      <color indexed="8"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Cambria"/>
@@ -254,6 +246,22 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="3" tint="0.59999389629810485"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -515,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -550,9 +558,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -592,12 +597,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -613,8 +618,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -625,9 +642,27 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -640,13 +675,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -655,7 +684,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -679,22 +708,43 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -706,74 +756,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1251,18 +1262,18 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="55" t="s">
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="56"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="70"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
     </row>
@@ -1274,18 +1285,18 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="57" t="s">
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
     </row>
@@ -1297,18 +1308,18 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="59" t="s">
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
     </row>
@@ -1320,18 +1331,18 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="65" t="s">
+      <c r="I8" s="68"/>
+      <c r="J8" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
     </row>
@@ -1343,14 +1354,14 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="25"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="24"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
     </row>
@@ -1364,18 +1375,18 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="74"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="75" t="s">
+      <c r="I10" s="68"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="O10" s="85"/>
+      <c r="O10" s="35"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
     </row>
@@ -1387,18 +1398,18 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="74" t="s">
+      <c r="H11" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="74"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="75" t="s">
+      <c r="I11" s="68"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="86"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
     </row>
@@ -1422,149 +1433,149 @@
     </row>
     <row r="13" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="76"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="77" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="77"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="78" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="12"/>
+      <c r="O15" s="36"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
     </row>
     <row r="16" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
     </row>
     <row r="17" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="79" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="31"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="32"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="31"/>
       <c r="Q18" s="2"/>
     </row>
     <row r="19" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="83" t="s">
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="78" t="s">
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="O19" s="78" t="s">
+      <c r="O19" s="34" t="s">
         <v>15</v>
       </c>
       <c r="P19" s="9"/>
@@ -1572,117 +1583,117 @@
     </row>
     <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="23"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="22"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="21"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="21"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="20"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="21"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="82"/>
+      <c r="K23" s="82"/>
+      <c r="L23" s="82"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="20"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
     </row>
@@ -1707,209 +1718,209 @@
     </row>
     <row r="27" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="70"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
     </row>
     <row r="28" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="77" t="s">
+      <c r="C28" s="42"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="77"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="69"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="44"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
     </row>
     <row r="29" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
     </row>
     <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
     </row>
     <row r="31" spans="1:17" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
     </row>
     <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="41"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="50"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="84" t="s">
+      <c r="B33" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
-      <c r="G33" s="84"/>
-      <c r="H33" s="84"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
-      <c r="N33" s="37"/>
-      <c r="O33" s="35"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="38"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="84" t="s">
+      <c r="B34" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="84"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="84"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="39"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="48"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="35"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="38"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="84"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
     </row>
@@ -1955,17 +1966,17 @@
       <c r="A39" s="8"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="20"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="29"/>
+      <c r="F39" s="28"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
@@ -1974,21 +1985,21 @@
       <c r="A40" s="8"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="16"/>
+      <c r="D40" s="15"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="34" t="s">
+      <c r="K40" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
+      <c r="L40" s="37"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="37"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
@@ -2013,22 +2024,22 @@
       <c r="Q41" s="2"/>
     </row>
     <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="17"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="19"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="18"/>
       <c r="Q42" s="2"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2147,11 +2158,12 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="E21:M21"/>
     <mergeCell ref="E22:M22"/>
     <mergeCell ref="E23:M23"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:M15"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="H10:I10"/>
@@ -2166,8 +2178,6 @@
     <mergeCell ref="J10:M10"/>
     <mergeCell ref="J8:O8"/>
     <mergeCell ref="H9:I9"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:M15"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B13:O13"/>
     <mergeCell ref="B16:O16"/>
@@ -2183,6 +2193,12 @@
     <mergeCell ref="D27:O27"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="B25:O25"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="K39:N39"/>
     <mergeCell ref="B30:O30"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B34:H34"/>
@@ -2190,11 +2206,6 @@
     <mergeCell ref="I34:O34"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="I32:O32"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="K39:N39"/>
     <mergeCell ref="K40:N40"/>
     <mergeCell ref="I36:O36"/>
     <mergeCell ref="B35:H35"/>

--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felp\Documents\viatop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trans\Documents\GitHub\repo-viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6575F1-0E79-4393-BC17-9E63E7D70BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8655A53-1AD1-4B8E-97A8-2231FCC56977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ficha Cadastral" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,15 +249,7 @@
     <font>
       <b/>
       <sz val="10.5"/>
-      <color theme="4" tint="-0.249977111117893"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color theme="3" tint="0.59999389629810485"/>
+      <color theme="3" tint="0.39997558519241921"/>
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
@@ -523,7 +515,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -633,157 +625,154 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1262,18 +1251,18 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="69" t="s">
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="70"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="47"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
     </row>
@@ -1285,18 +1274,18 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="71" t="s">
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
     </row>
@@ -1308,18 +1297,18 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="73" t="s">
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
     </row>
@@ -1331,18 +1320,18 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="68" t="s">
+      <c r="H8" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="68"/>
-      <c r="J8" s="79" t="s">
+      <c r="I8" s="45"/>
+      <c r="J8" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="80"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
     </row>
@@ -1354,11 +1343,11 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
       <c r="J9" s="25"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
       <c r="M9" s="2"/>
       <c r="N9" s="26"/>
       <c r="O9" s="24"/>
@@ -1375,14 +1364,14 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="68"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="78"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="53"/>
       <c r="N10" s="33" t="s">
         <v>12</v>
       </c>
@@ -1398,14 +1387,14 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="68"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="77"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="37"/>
       <c r="N11" s="33" t="s">
         <v>5</v>
       </c>
@@ -1433,22 +1422,22 @@
     </row>
     <row r="13" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
     </row>
@@ -1473,22 +1462,22 @@
     </row>
     <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="42" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="85"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="43"/>
       <c r="N15" s="34" t="s">
         <v>11</v>
       </c>
@@ -1498,56 +1487,56 @@
     </row>
     <row r="16" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
     </row>
     <row r="17" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
       <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="29"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21"/>
@@ -1556,22 +1545,22 @@
     </row>
     <row r="19" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="62" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
       <c r="N19" s="34" t="s">
         <v>24</v>
       </c>
@@ -1583,18 +1572,18 @@
     </row>
     <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="67"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="75"/>
       <c r="N20" s="27"/>
       <c r="O20" s="22"/>
       <c r="P20" s="9"/>
@@ -1602,18 +1591,18 @@
     </row>
     <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="75"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="39"/>
       <c r="N21" s="20"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
@@ -1621,18 +1610,18 @@
     </row>
     <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="75"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="39"/>
       <c r="N22" s="20"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
@@ -1640,18 +1629,18 @@
     </row>
     <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="82"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="75"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="39"/>
       <c r="N23" s="20"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
@@ -1678,22 +1667,22 @@
     </row>
     <row r="25" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="61"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
     </row>
@@ -1718,45 +1707,45 @@
     </row>
     <row r="27" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="64"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
     </row>
     <row r="28" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="87"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="86"/>
       <c r="E28" s="86"/>
       <c r="F28" s="86"/>
       <c r="G28" s="86"/>
       <c r="H28" s="86"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="K28" s="42" t="s">
+      <c r="K28" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="42"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="44"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="70"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
     </row>
@@ -1781,22 +1770,22 @@
     </row>
     <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
     </row>
@@ -1821,106 +1810,106 @@
     </row>
     <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="50"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
+      <c r="M32" s="83"/>
+      <c r="N32" s="83"/>
+      <c r="O32" s="84"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="38"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="80"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="81"/>
+      <c r="N34" s="81"/>
+      <c r="O34" s="82"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="38"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="80"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="85"/>
+      <c r="L36" s="85"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
     </row>
@@ -1973,10 +1962,10 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
@@ -1994,12 +1983,12 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="37" t="s">
+      <c r="K40" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
@@ -2158,26 +2147,23 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:O32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B13:O13"/>
     <mergeCell ref="B16:O16"/>
@@ -2194,23 +2180,26 @@
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="B25:O25"/>
     <mergeCell ref="E21:M21"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:M15"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trans\Documents\GitHub\repo-viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8655A53-1AD1-4B8E-97A8-2231FCC56977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC08263-DF98-458C-BFA3-DE20E17D1A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ficha Cadastral" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>CARGA</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>REMETENTE/DESTINATÁRIO</t>
+  </si>
+  <si>
+    <t>ORDEM</t>
   </si>
 </sst>
 </file>
@@ -571,9 +574,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -625,128 +625,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -754,8 +640,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -769,10 +670,112 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -809,8 +812,8 @@
       <xdr:rowOff>57442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>132470</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>846845</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>41310</xdr:rowOff>
     </xdr:to>
@@ -1150,7 +1153,7 @@
     <col min="1" max="1" width="5.28515625" style="10" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" style="10" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12" style="10" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" style="10" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" style="10" customWidth="1"/>
     <col min="7" max="7" width="4.42578125" style="10" customWidth="1"/>
@@ -1251,18 +1254,18 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="46" t="s">
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="47"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="73"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
     </row>
@@ -1274,18 +1277,18 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="48" t="s">
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="75"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
     </row>
@@ -1297,18 +1300,18 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="50" t="s">
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
     </row>
@@ -1320,18 +1323,18 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="54" t="s">
+      <c r="I8" s="71"/>
+      <c r="J8" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="55"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="75"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
     </row>
@@ -1343,14 +1346,14 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
     </row>
@@ -1364,18 +1367,18 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="33" t="s">
+      <c r="I10" s="71"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="O10" s="35"/>
+      <c r="O10" s="34"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
     </row>
@@ -1387,18 +1390,18 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="33" t="s">
+      <c r="I11" s="71"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="32"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
     </row>
@@ -1422,149 +1425,149 @@
     </row>
     <row r="13" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="57"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="40" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="34" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="36"/>
+      <c r="O15" s="35"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
     </row>
     <row r="16" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
     </row>
     <row r="17" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="61" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="30"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="29"/>
     </row>
     <row r="18" spans="1:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="31"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="30"/>
       <c r="Q18" s="2"/>
     </row>
     <row r="19" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="69" t="s">
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="34" t="s">
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="O19" s="34" t="s">
+      <c r="O19" s="33" t="s">
         <v>15</v>
       </c>
       <c r="P19" s="9"/>
@@ -1572,76 +1575,76 @@
     </row>
     <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="75"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="22"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="21"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="20"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="20"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="20"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="19"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
@@ -1667,22 +1670,22 @@
     </row>
     <row r="25" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="61"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
     </row>
@@ -1707,45 +1710,45 @@
     </row>
     <row r="27" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
     </row>
     <row r="28" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="40" t="s">
+      <c r="C28" s="42"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="40"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="70"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="44"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
     </row>
@@ -1770,22 +1773,22 @@
     </row>
     <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
     </row>
@@ -1810,106 +1813,106 @@
     </row>
     <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="50"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="80"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="37"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="81"/>
-      <c r="N34" s="81"/>
-      <c r="O34" s="82"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+      <c r="N34" s="47"/>
+      <c r="O34" s="48"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="78" t="s">
+      <c r="B35" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="79"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="79"/>
-      <c r="M35" s="79"/>
-      <c r="N35" s="79"/>
-      <c r="O35" s="80"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="37"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="78" t="s">
+      <c r="B36" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="80"/>
-      <c r="K36" s="85"/>
-      <c r="L36" s="85"/>
-      <c r="M36" s="85"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
     </row>
@@ -1953,19 +1956,21 @@
     </row>
     <row r="39" spans="1:17" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="19"/>
+      <c r="B39" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="42"/>
+      <c r="D39" s="86"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="28"/>
+      <c r="F39" s="27"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
@@ -1983,12 +1988,12 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="44" t="s">
+      <c r="K40" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
@@ -2146,24 +2151,27 @@
       <c r="Q48" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:O32"/>
+  <mergeCells count="54">
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B13:O13"/>
     <mergeCell ref="B16:O16"/>
@@ -2180,30 +2188,28 @@
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="B25:O25"/>
     <mergeCell ref="E21:M21"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="73" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ordemagroviav2.xlsx
+++ b/ordemagroviav2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trans\Documents\GitHub\repo-viatop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC08263-DF98-458C-BFA3-DE20E17D1A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AA9BBE-A6A2-407A-B7D2-E3B896887085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -625,158 +625,158 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1254,18 +1254,18 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="71" t="s">
+      <c r="H5" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="72" t="s">
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="73"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="47"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
     </row>
@@ -1277,18 +1277,18 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="71" t="s">
+      <c r="H6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="74" t="s">
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
     </row>
@@ -1300,18 +1300,18 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="76" t="s">
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
     </row>
@@ -1323,18 +1323,18 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="71" t="s">
+      <c r="H8" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="71"/>
-      <c r="J8" s="80" t="s">
+      <c r="I8" s="45"/>
+      <c r="J8" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="81"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75"/>
-      <c r="N8" s="75"/>
-      <c r="O8" s="75"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
     </row>
@@ -1346,11 +1346,11 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
       <c r="M9" s="2"/>
       <c r="N9" s="25"/>
       <c r="O9" s="23"/>
@@ -1367,14 +1367,14 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="71" t="s">
+      <c r="H10" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="79"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="53"/>
       <c r="N10" s="32" t="s">
         <v>12</v>
       </c>
@@ -1390,14 +1390,14 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="71" t="s">
+      <c r="H11" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="71"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="68"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="37"/>
       <c r="N11" s="32" t="s">
         <v>5</v>
       </c>
@@ -1425,22 +1425,22 @@
     </row>
     <row r="13" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
     </row>
@@ -1465,22 +1465,22 @@
     </row>
     <row r="15" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="42" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="85"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="43"/>
       <c r="N15" s="33" t="s">
         <v>11</v>
       </c>
@@ -1490,56 +1490,56 @@
     </row>
     <row r="16" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
     </row>
     <row r="17" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
       <c r="P17" s="29"/>
     </row>
     <row r="18" spans="1:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="54"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
       <c r="O18" s="20"/>
@@ -1548,22 +1548,22 @@
     </row>
     <row r="19" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="62" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
       <c r="N19" s="33" t="s">
         <v>24</v>
       </c>
@@ -1575,18 +1575,18 @@
     </row>
     <row r="20" spans="1:17" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="67"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="75"/>
       <c r="N20" s="26"/>
       <c r="O20" s="21"/>
       <c r="P20" s="9"/>
@@ -1594,18 +1594,18 @@
     </row>
     <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="70"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="39"/>
       <c r="N21" s="19"/>
       <c r="O21" s="3"/>
       <c r="P21" s="9"/>
@@ -1613,18 +1613,18 @@
     </row>
     <row r="22" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="70"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="39"/>
       <c r="N22" s="19"/>
       <c r="O22" s="3"/>
       <c r="P22" s="9"/>
@@ -1632,18 +1632,18 @@
     </row>
     <row r="23" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="70"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="39"/>
       <c r="N23" s="19"/>
       <c r="O23" s="3"/>
       <c r="P23" s="9"/>
@@ -1670,22 +1670,22 @@
     </row>
     <row r="25" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="61"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
     </row>
@@ -1710,45 +1710,45 @@
     </row>
     <row r="27" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="64"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
     </row>
     <row r="28" spans="1:17" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="42" t="s">
+      <c r="C28" s="40"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="42"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="44"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="77"/>
+      <c r="N28" s="77"/>
+      <c r="O28" s="70"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
     </row>
@@ -1773,22 +1773,22 @@
     </row>
     <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
     </row>
@@ -1813,106 +1813,106 @@
     </row>
     <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="50"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="85"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="37"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="81"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="83"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="37"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="81"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="86"/>
+      <c r="M36" s="86"/>
+      <c r="N36" s="86"/>
+      <c r="O36" s="86"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
     </row>
@@ -1956,21 +1956,21 @@
     </row>
     <row r="39" spans="1:17" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="36"/>
       <c r="E39" s="2"/>
       <c r="F39" s="27"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+      <c r="M39" s="78"/>
+      <c r="N39" s="78"/>
       <c r="O39" s="2"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
@@ -1988,12 +1988,12 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="36" t="s">
+      <c r="K40" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
       <c r="O40" s="2"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
@@ -2152,26 +2152,24 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B13:O13"/>
     <mergeCell ref="B16:O16"/>
@@ -2188,24 +2186,26 @@
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="B25:O25"/>
     <mergeCell ref="E21:M21"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:M15"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
